--- a/POTAL_B2B_Checklist.xlsx
+++ b/POTAL_B2B_Checklist.xlsx
@@ -1286,7 +1286,7 @@
       </c>
       <c r="F12" s="30" t="inlineStr">
         <is>
-          <t>TODO</t>
+          <t>✅ Done</t>
         </is>
       </c>
       <c r="G12" s="25" t="inlineStr">
@@ -1301,7 +1301,7 @@
       </c>
       <c r="I12" s="22" t="inlineStr">
         <is>
-          <t>GPT-4o-mini + 공개 HS Code DB. 상품명/카테고리 → HS Code + 관세율</t>
+          <t>GPT-4o-mini AI 분류 + DB캐싱 + 키워드 매칭. ai-classifier-wrapper.ts</t>
         </is>
       </c>
     </row>
@@ -1333,7 +1333,7 @@
       </c>
       <c r="F13" s="30" t="inlineStr">
         <is>
-          <t>TODO</t>
+          <t>✅ Done</t>
         </is>
       </c>
       <c r="G13" s="29" t="inlineStr">
@@ -1348,7 +1348,7 @@
       </c>
       <c r="I13" s="28" t="inlineStr">
         <is>
-          <t>국가코드 + HS Code(선택) → 관세율, VAT/GST, de minimis 기준</t>
+          <t>/api/v1/countries에서 세율 정보 제공. 139개국 데이터</t>
         </is>
       </c>
     </row>
@@ -1474,7 +1474,7 @@
       </c>
       <c r="F16" s="30" t="inlineStr">
         <is>
-          <t>TODO</t>
+          <t>✅ Done</t>
         </is>
       </c>
       <c r="G16" s="25" t="inlineStr">
@@ -1489,7 +1489,7 @@
       </c>
       <c r="I16" s="22" t="inlineStr">
         <is>
-          <t>HTS 공개 데이터 기반. Chapter 1~97</t>
+          <t>USITC REST API 연동 (usitc-provider.ts). 실시간 조회</t>
         </is>
       </c>
     </row>
@@ -1568,7 +1568,7 @@
       </c>
       <c r="F18" s="30" t="inlineStr">
         <is>
-          <t>TODO</t>
+          <t>✅ Done</t>
         </is>
       </c>
       <c r="G18" s="25" t="inlineStr">
@@ -1583,7 +1583,7 @@
       </c>
       <c r="I18" s="28" t="inlineStr">
         <is>
-          <t>표준세율 + 경감세율. AT~SE 27국</t>
+          <t>EU TARIC API 연동 (eu-taric-provider.ts). CET 파싱</t>
         </is>
       </c>
     </row>
@@ -1615,7 +1615,7 @@
       </c>
       <c r="F19" s="30" t="inlineStr">
         <is>
-          <t>TODO</t>
+          <t>✅ Done</t>
         </is>
       </c>
       <c r="G19" s="25" t="inlineStr">
@@ -1630,7 +1630,7 @@
       </c>
       <c r="I19" s="22" t="inlineStr">
         <is>
-          <t>Common External Tariff. TARIC 공개 DB</t>
+          <t>EU TARIC API에서 27개국 VAT 데이터 제공</t>
         </is>
       </c>
     </row>
@@ -1662,7 +1662,7 @@
       </c>
       <c r="F20" s="30" t="inlineStr">
         <is>
-          <t>TODO</t>
+          <t>✅ Done</t>
         </is>
       </c>
       <c r="G20" s="25" t="inlineStr">
@@ -1677,7 +1677,7 @@
       </c>
       <c r="I20" s="22" t="inlineStr">
         <is>
-          <t>VAT 20% 표준, UK Global Tariff</t>
+          <t>UK Trade Tariff API 연동 (uk-tariff-provider.ts). MFN 파싱</t>
         </is>
       </c>
     </row>
@@ -2273,7 +2273,7 @@
       </c>
       <c r="F33" s="30" t="inlineStr">
         <is>
-          <t>TODO</t>
+          <t>✅ Done</t>
         </is>
       </c>
       <c r="G33" s="25" t="inlineStr">
@@ -2288,7 +2288,7 @@
       </c>
       <c r="I33" s="28" t="inlineStr">
         <is>
-          <t>무료 API (exchangerate-api 또는 frankfurter). 캐시 1시간</t>
+          <t>ExchangeRate-API + Fawaz CDN 이중 폴백. exchange-rate-service.ts</t>
         </is>
       </c>
     </row>
@@ -2320,7 +2320,7 @@
       </c>
       <c r="F34" s="30" t="inlineStr">
         <is>
-          <t>TODO</t>
+          <t>✅ Done</t>
         </is>
       </c>
       <c r="G34" s="25" t="inlineStr">
@@ -2335,7 +2335,7 @@
       </c>
       <c r="I34" s="22" t="inlineStr">
         <is>
-          <t>ISO 4217 코드 지원. 150+ 통화</t>
+          <t>166+ 통화 지원. exchange-rate-service.ts에 통합</t>
         </is>
       </c>
     </row>
@@ -2414,7 +2414,7 @@
       </c>
       <c r="F36" s="30" t="inlineStr">
         <is>
-          <t>TODO</t>
+          <t>✅ Done</t>
         </is>
       </c>
       <c r="G36" s="25" t="inlineStr">
@@ -2429,7 +2429,7 @@
       </c>
       <c r="I36" s="28" t="inlineStr">
         <is>
-          <t>국가별 관세율 데이터에서 HS Code로 조회</t>
+          <t>AI 분류 + 외부 API (USITC/UK/EU) 조합으로 HS→관세율 매핑</t>
         </is>
       </c>
     </row>
@@ -2461,7 +2461,7 @@
       </c>
       <c r="F37" s="30" t="inlineStr">
         <is>
-          <t>TODO</t>
+          <t>✅ Done</t>
         </is>
       </c>
       <c r="G37" s="29" t="inlineStr">
@@ -2476,7 +2476,7 @@
       </c>
       <c r="I37" s="22" t="inlineStr">
         <is>
-          <t>USMCA, EU-KR, RCEP, CPTPP 등 주요 FTA 우대세율</t>
+          <t>27개 FTA 적용. fta-agreements.ts</t>
         </is>
       </c>
     </row>
@@ -2649,7 +2649,7 @@
       </c>
       <c r="F41" s="30" t="inlineStr">
         <is>
-          <t>TODO</t>
+          <t>✅ Done</t>
         </is>
       </c>
       <c r="G41" s="25" t="inlineStr">
@@ -2664,7 +2664,7 @@
       </c>
       <c r="I41" s="22" t="inlineStr">
         <is>
-          <t>US, EU, UK, JP, KR, AU, CA 각 1개씩 시나리오</t>
+          <t>__tests__/api/cost-engine.test.ts 작성 완료</t>
         </is>
       </c>
     </row>
@@ -3534,7 +3534,7 @@
       </c>
       <c r="F60" s="30" t="inlineStr">
         <is>
-          <t>TODO</t>
+          <t>✅ Done</t>
         </is>
       </c>
       <c r="G60" s="25" t="inlineStr">
@@ -3549,7 +3549,7 @@
       </c>
       <c r="I60" s="22" t="inlineStr">
         <is>
-          <t>partners.shopify.com</t>
+          <t>Shopify Partner Dashboard 등록 완료. Client ID: 2fa34ed65342ffb7fac08dd916f470b8</t>
         </is>
       </c>
     </row>
@@ -3581,7 +3581,7 @@
       </c>
       <c r="F61" s="30" t="inlineStr">
         <is>
-          <t>TODO</t>
+          <t>✅ Done</t>
         </is>
       </c>
       <c r="G61" s="25" t="inlineStr">
@@ -3596,7 +3596,7 @@
       </c>
       <c r="I61" s="22" t="inlineStr">
         <is>
-          <t>Shopify CLI + Remix 템플릿</t>
+          <t>Shopify CLI + shopify.app.toml 설정 완료</t>
         </is>
       </c>
     </row>
@@ -3628,7 +3628,7 @@
       </c>
       <c r="F62" s="30" t="inlineStr">
         <is>
-          <t>TODO</t>
+          <t>✅ Done</t>
         </is>
       </c>
       <c r="G62" s="25" t="inlineStr">
@@ -3643,7 +3643,7 @@
       </c>
       <c r="I62" s="28" t="inlineStr">
         <is>
-          <t>설치 → 권한 동의 → 콜백 → seller 등록</t>
+          <t>OAuth managed install flow. app/api/shopify/auth+callback. host→shop 추출</t>
         </is>
       </c>
     </row>
@@ -3675,7 +3675,7 @@
       </c>
       <c r="F63" s="30" t="inlineStr">
         <is>
-          <t>TODO</t>
+          <t>✅ Done</t>
         </is>
       </c>
       <c r="G63" s="25" t="inlineStr">
@@ -3690,7 +3690,7 @@
       </c>
       <c r="I63" s="22" t="inlineStr">
         <is>
-          <t>Script Tag 또는 App Block</t>
+          <t>Theme App Extension 3블록 (상품위젯/장바구니배너/앱임베드). potal-3 릴리스</t>
         </is>
       </c>
     </row>
@@ -3722,7 +3722,7 @@
       </c>
       <c r="F64" s="30" t="inlineStr">
         <is>
-          <t>TODO</t>
+          <t>✅ Done</t>
         </is>
       </c>
       <c r="G64" s="25" t="inlineStr">
@@ -3737,7 +3737,7 @@
       </c>
       <c r="I64" s="28" t="inlineStr">
         <is>
-          <t>앱 리스팅, 스크린샷, 설명</t>
+          <t>앱 리스팅 전체 작성 + $19 결제 + 예비 단계 8/9. 임베디드 확인 대기</t>
         </is>
       </c>
     </row>
@@ -3910,7 +3910,7 @@
       </c>
       <c r="F68" s="30" t="inlineStr">
         <is>
-          <t>TODO</t>
+          <t>✅ Done</t>
         </is>
       </c>
       <c r="G68" s="25" t="inlineStr">
@@ -3925,7 +3925,7 @@
       </c>
       <c r="I68" s="22" t="inlineStr">
         <is>
-          <t>allowed_domains 체크</t>
+          <t>CORS 설정 완료. widget.js HTTP 200 + Access-Control-Allow-Origin</t>
         </is>
       </c>
     </row>
@@ -4192,7 +4192,7 @@
       </c>
       <c r="F74" s="30" t="inlineStr">
         <is>
-          <t>TODO</t>
+          <t>✅ Done</t>
         </is>
       </c>
       <c r="G74" s="25" t="inlineStr">
@@ -4207,7 +4207,7 @@
       </c>
       <c r="I74" s="22" t="inlineStr">
         <is>
-          <t>Stripe Dashboard → API Keys</t>
+          <t>Stripe 계정 가입 (Wise USD). Test mode API 키 설정 완료</t>
         </is>
       </c>
     </row>
@@ -4239,7 +4239,7 @@
       </c>
       <c r="F75" s="30" t="inlineStr">
         <is>
-          <t>TODO</t>
+          <t>✅ Done</t>
         </is>
       </c>
       <c r="G75" s="25" t="inlineStr">
@@ -4254,7 +4254,7 @@
       </c>
       <c r="I75" s="22" t="inlineStr">
         <is>
-          <t>Starter/Growth/Enterprise 3개 plan</t>
+          <t>POTAL Growth $49/month product 생성 완료</t>
         </is>
       </c>
     </row>
@@ -4286,7 +4286,7 @@
       </c>
       <c r="F76" s="30" t="inlineStr">
         <is>
-          <t>TODO</t>
+          <t>✅ Done</t>
         </is>
       </c>
       <c r="G76" s="25" t="inlineStr">
@@ -4301,7 +4301,7 @@
       </c>
       <c r="I76" s="22" t="inlineStr">
         <is>
-          <t>14일 무료 체험 → 자동 과금 전환</t>
+          <t>app/api/billing/checkout/route.ts 완료</t>
         </is>
       </c>
     </row>
@@ -4333,7 +4333,7 @@
       </c>
       <c r="F77" s="30" t="inlineStr">
         <is>
-          <t>TODO</t>
+          <t>✅ Done</t>
         </is>
       </c>
       <c r="G77" s="25" t="inlineStr">
@@ -4348,7 +4348,7 @@
       </c>
       <c r="I77" s="22" t="inlineStr">
         <is>
-          <t>subscription.created/updated/deleted → sellers 테이블 업데이트</t>
+          <t>app/api/billing/webhook/route.ts 6개 이벤트 처리</t>
         </is>
       </c>
     </row>
@@ -4380,7 +4380,7 @@
       </c>
       <c r="F78" s="30" t="inlineStr">
         <is>
-          <t>TODO</t>
+          <t>✅ Done</t>
         </is>
       </c>
       <c r="G78" s="25" t="inlineStr">
@@ -4393,7 +4393,11 @@
           <t>2h</t>
         </is>
       </c>
-      <c r="I78" s="22" t="n"/>
+      <c r="I78" s="22" t="inlineStr">
+        <is>
+          <t>app/lib/billing/subscription.ts 라이프사이클 관리</t>
+        </is>
+      </c>
     </row>
     <row r="79" ht="15" customHeight="1" s="19">
       <c r="A79" s="35" t="inlineStr">
@@ -4470,7 +4474,7 @@
       </c>
       <c r="F80" s="30" t="inlineStr">
         <is>
-          <t>TODO</t>
+          <t>✅ Done</t>
         </is>
       </c>
       <c r="G80" s="25" t="inlineStr">
@@ -4485,7 +4489,7 @@
       </c>
       <c r="I80" s="28" t="inlineStr">
         <is>
-          <t>이번 달 계산 횟수, 남은 한도, 플랜 정보</t>
+          <t>Dashboard Overview/API Keys/Widget/Usage/Billing 5탭 완료</t>
         </is>
       </c>
     </row>
@@ -4611,7 +4615,7 @@
       </c>
       <c r="F83" s="30" t="inlineStr">
         <is>
-          <t>TODO</t>
+          <t>✅ Done</t>
         </is>
       </c>
       <c r="G83" s="25" t="inlineStr">
@@ -4626,7 +4630,7 @@
       </c>
       <c r="I83" s="22" t="inlineStr">
         <is>
-          <t>Stripe Customer Portal 연동</t>
+          <t>Stripe Customer Portal 연동 완료</t>
         </is>
       </c>
     </row>
@@ -5379,10 +5383,10 @@
         <v>38</v>
       </c>
       <c r="C3" s="23" t="n">
-        <v>1</v>
+        <v>24</v>
       </c>
       <c r="D3" s="23" t="n">
-        <v>37</v>
+        <v>14</v>
       </c>
       <c r="E3" s="23" t="inlineStr">
         <is>
@@ -5400,10 +5404,10 @@
         <v>17</v>
       </c>
       <c r="C4" s="23" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="D4" s="23" t="n">
-        <v>17</v>
+        <v>7</v>
       </c>
       <c r="E4" s="23" t="inlineStr">
         <is>
@@ -5421,10 +5425,10 @@
         <v>14</v>
       </c>
       <c r="C5" s="23" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="D5" s="23" t="n">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="E5" s="23" t="inlineStr">
         <is>
@@ -5442,10 +5446,10 @@
         <v>11</v>
       </c>
       <c r="C6" s="23" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="D6" s="23" t="n">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="E6" s="23" t="inlineStr">
         <is>

--- a/POTAL_B2B_Checklist.xlsx
+++ b/POTAL_B2B_Checklist.xlsx
@@ -1207,7 +1207,7 @@
       </c>
       <c r="I10" s="22" t="inlineStr">
         <is>
-          <t>calculateGlobalLandedCostAsync. 139개국 지원</t>
+          <t>calculateGlobalLandedCostAsync. 181개국 지원</t>
         </is>
       </c>
     </row>
@@ -1348,7 +1348,7 @@
       </c>
       <c r="I13" s="28" t="inlineStr">
         <is>
-          <t>/api/v1/countries에서 세율 정보 제공. 139개국 데이터</t>
+          <t>/api/v1/countries에서 세율 정보 제공. 181개국 데이터</t>
         </is>
       </c>
     </row>
@@ -1709,7 +1709,7 @@
       </c>
       <c r="F21" s="30" t="inlineStr">
         <is>
-          <t>TODO</t>
+          <t>✅ Done</t>
         </is>
       </c>
       <c r="G21" s="29" t="inlineStr">
@@ -1724,7 +1724,7 @@
       </c>
       <c r="I21" s="28" t="inlineStr">
         <is>
-          <t>소비세 10% (식품 8%), Japan Customs Tariff Schedule</t>
+          <t>Japan Customs Provider (japan-customs-provider.ts) 추가 완료. 세션 25</t>
         </is>
       </c>
     </row>
@@ -1756,7 +1756,7 @@
       </c>
       <c r="F22" s="30" t="inlineStr">
         <is>
-          <t>TODO</t>
+          <t>✅ Done</t>
         </is>
       </c>
       <c r="G22" s="29" t="inlineStr">
@@ -1771,7 +1771,7 @@
       </c>
       <c r="I22" s="28" t="inlineStr">
         <is>
-          <t>부가세 10%, 관세법 별표. 관세청 공개 데이터</t>
+          <t>Korea KCS Provider (korea-kcs-provider.ts) 추가 완료. 세션 25</t>
         </is>
       </c>
     </row>
@@ -1803,7 +1803,7 @@
       </c>
       <c r="F23" s="30" t="inlineStr">
         <is>
-          <t>TODO</t>
+          <t>✅ Done</t>
         </is>
       </c>
       <c r="G23" s="29" t="inlineStr">
@@ -1818,7 +1818,7 @@
       </c>
       <c r="I23" s="22" t="inlineStr">
         <is>
-          <t>GST 10%, Australian Customs Tariff</t>
+          <t>Australia ABF Provider (australia-abf-provider.ts) 추가 완료. GST 10%. 세션 25</t>
         </is>
       </c>
     </row>
@@ -1850,7 +1850,7 @@
       </c>
       <c r="F24" s="30" t="inlineStr">
         <is>
-          <t>TODO</t>
+          <t>✅ Done</t>
         </is>
       </c>
       <c r="G24" s="29" t="inlineStr">
@@ -1865,7 +1865,7 @@
       </c>
       <c r="I24" s="28" t="inlineStr">
         <is>
-          <t>연방 GST 5% + 주별 PST/HST 가변</t>
+          <t>Canada CBSA Provider (canada-cbsa-provider.ts) 추가 완료. GST 5% + 주별 PST/HST. 세션 25</t>
         </is>
       </c>
     </row>
@@ -1944,7 +1944,7 @@
       </c>
       <c r="F26" s="30" t="inlineStr">
         <is>
-          <t>TODO</t>
+          <t>✅ Done</t>
         </is>
       </c>
       <c r="G26" s="29" t="inlineStr">
@@ -1959,7 +1959,7 @@
       </c>
       <c r="I26" s="22" t="inlineStr">
         <is>
-          <t>GST 5~28%, Basic Customs Duty</t>
+          <t>India 세금 구현 완료: BCD + SWS(10%) + IGST(5-28%) 캐스케이딩. 세션 25</t>
         </is>
       </c>
     </row>
@@ -2241,7 +2241,7 @@
       </c>
       <c r="I32" s="22" t="inlineStr">
         <is>
-          <t>country-data.ts에 139개국 deMinimisUsd 포함</t>
+          <t>country-data.ts에 181개국 deMinimisUsd 포함</t>
         </is>
       </c>
     </row>
@@ -2382,7 +2382,7 @@
       </c>
       <c r="I35" s="28" t="inlineStr">
         <is>
-          <t>GlobalCostEngine.ts. 139개국 DB-backed + fallback hardcoded data</t>
+          <t>GlobalCostEngine.ts. 181개국 DB-backed + fallback hardcoded data. India/Brazil 특수 세금</t>
         </is>
       </c>
     </row>
@@ -2476,7 +2476,7 @@
       </c>
       <c r="I37" s="22" t="inlineStr">
         <is>
-          <t>27개 FTA 적용. fta-agreements.ts</t>
+          <t>63개 FTA 적용. fta-agreements.ts. 세션 25에서 확장</t>
         </is>
       </c>
     </row>
@@ -2602,7 +2602,7 @@
       </c>
       <c r="F40" s="30" t="inlineStr">
         <is>
-          <t>TODO</t>
+          <t>✅ Done</t>
         </is>
       </c>
       <c r="G40" s="31" t="inlineStr">
@@ -2617,7 +2617,7 @@
       </c>
       <c r="I40" s="22" t="inlineStr">
         <is>
-          <t>swagger-ui-react 사용. 셀러가 바로 테스트</t>
+          <t>/developers/docs Swagger UI 스타일 재구축 완료. 6개 엔드포인트, Try it, cURL/JS/Python. 세션 24</t>
         </is>
       </c>
     </row>
@@ -2993,7 +2993,7 @@
       </c>
       <c r="I48" s="22" t="inlineStr">
         <is>
-          <t>Gemini Gem 생성 완료. 지침 + country-duty-reference.csv 업로드</t>
+          <t>Gemini Gem 생성 완료. 지침 + country-duty-reference.csv (181개국) 업로드. 세션 26 업데이트</t>
         </is>
       </c>
     </row>
@@ -3737,7 +3737,7 @@
       </c>
       <c r="I64" s="28" t="inlineStr">
         <is>
-          <t>앱 리스팅 전체 작성 + $19 결제 + 예비 단계 8/9. 임베디드 확인 대기</t>
+          <t>앱 리스팅 전체 작성 + $19 결제 + 예비 단계 8/9. App Bridge push 완료, 임베디드 확인 대기</t>
         </is>
       </c>
     </row>
@@ -3831,7 +3831,7 @@
       </c>
       <c r="I66" s="22" t="inlineStr">
         <is>
-          <t>iframe/Shadow DOM. 139개국 hardcoded. breakdown 표시</t>
+          <t>iframe/Shadow DOM. 181개국 hardcoded. breakdown 표시</t>
         </is>
       </c>
     </row>
@@ -4207,7 +4207,7 @@
       </c>
       <c r="I74" s="22" t="inlineStr">
         <is>
-          <t>Stripe 계정 가입 (Wise USD). Test mode API 키 설정 완료</t>
+          <t>⚠️ Stripe 계정 정지됨 (세션 26). Paddle/LemonSqueezy 전환 필요</t>
         </is>
       </c>
     </row>
@@ -4906,7 +4906,11 @@
           <t>4h</t>
         </is>
       </c>
-      <c r="I89" s="22" t="n"/>
+      <c r="I89" s="22" t="inlineStr">
+        <is>
+          <t>country-data.ts에 181개국 포함. TH/VN/PH/ID/MY/SG 모두 세율 데이터 있음</t>
+        </is>
+      </c>
     </row>
     <row r="90" ht="15" customHeight="1" s="19">
       <c r="A90" s="36" t="inlineStr">
@@ -4992,7 +4996,11 @@
           <t>4h</t>
         </is>
       </c>
-      <c r="I91" s="22" t="n"/>
+      <c r="I91" s="22" t="inlineStr">
+        <is>
+          <t>country-data.ts에 181개국 포함. BR/MX/AR/CL/CO 모두 세율 데이터 있음. Brazil ICMS/IPI 구현됨</t>
+        </is>
+      </c>
     </row>
     <row r="92" ht="15" customHeight="1" s="19">
       <c r="A92" s="36" t="inlineStr">
@@ -5035,7 +5043,11 @@
           <t>3h</t>
         </is>
       </c>
-      <c r="I92" s="22" t="n"/>
+      <c r="I92" s="22" t="inlineStr">
+        <is>
+          <t>country-data.ts에 181개국 포함. ZA/NG/KE/EG 모두 세율 데이터 있음</t>
+        </is>
+      </c>
     </row>
     <row r="93" ht="15" customHeight="1" s="19">
       <c r="A93" s="36" t="inlineStr">
@@ -5155,7 +5167,7 @@
       </c>
       <c r="F95" s="30" t="inlineStr">
         <is>
-          <t>TODO</t>
+          <t>✅ Done</t>
         </is>
       </c>
       <c r="G95" s="31" t="inlineStr">
@@ -5168,7 +5180,11 @@
           <t>4h</t>
         </is>
       </c>
-      <c r="I95" s="22" t="n"/>
+      <c r="I95" s="22" t="inlineStr">
+        <is>
+          <t>63개 FTA 확장 완료 (27→63). 세션 25</t>
+        </is>
+      </c>
     </row>
     <row r="96" ht="15" customHeight="1" s="19">
       <c r="A96" s="36" t="inlineStr">
@@ -5383,10 +5399,10 @@
         <v>38</v>
       </c>
       <c r="C3" s="23" t="n">
-        <v>24</v>
+        <v>33</v>
       </c>
       <c r="D3" s="23" t="n">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="E3" s="23" t="inlineStr">
         <is>
@@ -5407,7 +5423,7 @@
         <v>10</v>
       </c>
       <c r="D4" s="23" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="E4" s="23" t="inlineStr">
         <is>
@@ -5467,10 +5483,10 @@
         <v>14</v>
       </c>
       <c r="C7" s="23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D7" s="23" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="E7" s="23" t="inlineStr">
         <is>

--- a/POTAL_B2B_Checklist.xlsx
+++ b/POTAL_B2B_Checklist.xlsx
@@ -4172,7 +4172,7 @@
       </c>
       <c r="B74" s="22" t="inlineStr">
         <is>
-          <t>Stripe</t>
+          <t>LemonSqueezy</t>
         </is>
       </c>
       <c r="C74" s="23" t="inlineStr">
@@ -4182,7 +4182,7 @@
       </c>
       <c r="D74" s="22" t="inlineStr">
         <is>
-          <t>Stripe 계정 연동 + API 키 설정</t>
+          <t>LemonSqueezy 계정 설정 + Store 생성</t>
         </is>
       </c>
       <c r="E74" s="22" t="inlineStr">
@@ -4207,7 +4207,7 @@
       </c>
       <c r="I74" s="22" t="inlineStr">
         <is>
-          <t>⚠️ Stripe 계정 정지됨 (세션 26). Paddle/LemonSqueezy 전환 필요</t>
+          <t>✅ Stripe→LemonSqueezy 전환 완료 (세션 26). potalapp.lemonsqueezy.com Store #308025. 신원 확인 대기</t>
         </is>
       </c>
     </row>
@@ -4219,7 +4219,7 @@
       </c>
       <c r="B75" s="22" t="inlineStr">
         <is>
-          <t>Stripe</t>
+          <t>LemonSqueezy</t>
         </is>
       </c>
       <c r="C75" s="23" t="inlineStr">
@@ -4229,17 +4229,17 @@
       </c>
       <c r="D75" s="22" t="inlineStr">
         <is>
-          <t>Stripe Products + Prices 생성</t>
+          <t>LemonSqueezy Products + Variants 생성</t>
         </is>
       </c>
       <c r="E75" s="22" t="inlineStr">
         <is>
-          <t>app/lib/billing/stripe-setup.ts</t>
+          <t>LemonSqueezy Dashboard</t>
         </is>
       </c>
       <c r="F75" s="30" t="inlineStr">
         <is>
-          <t>✅ Done</t>
+          <t>TODO</t>
         </is>
       </c>
       <c r="G75" s="25" t="inlineStr">
@@ -4254,7 +4254,7 @@
       </c>
       <c r="I75" s="22" t="inlineStr">
         <is>
-          <t>POTAL Growth $49/month product 생성 완료</t>
+          <t>Starter $9, Growth $29, Enterprise custom. 신원 확인 승인 후 생성 가능</t>
         </is>
       </c>
     </row>
@@ -4266,7 +4266,7 @@
       </c>
       <c r="B76" s="22" t="inlineStr">
         <is>
-          <t>Stripe</t>
+          <t>LemonSqueezy</t>
         </is>
       </c>
       <c r="C76" s="23" t="inlineStr">
@@ -4276,7 +4276,7 @@
       </c>
       <c r="D76" s="22" t="inlineStr">
         <is>
-          <t>Stripe Checkout 세션 생성</t>
+          <t>LemonSqueezy Checkout 구현</t>
         </is>
       </c>
       <c r="E76" s="22" t="inlineStr">
@@ -4301,7 +4301,7 @@
       </c>
       <c r="I76" s="22" t="inlineStr">
         <is>
-          <t>app/api/billing/checkout/route.ts 완료</t>
+          <t>✅ app/api/billing/checkout/route.ts LemonSqueezy createCheckout() 전환 완료</t>
         </is>
       </c>
     </row>
@@ -4313,7 +4313,7 @@
       </c>
       <c r="B77" s="22" t="inlineStr">
         <is>
-          <t>Stripe</t>
+          <t>LemonSqueezy</t>
         </is>
       </c>
       <c r="C77" s="23" t="inlineStr">
@@ -4323,7 +4323,7 @@
       </c>
       <c r="D77" s="22" t="inlineStr">
         <is>
-          <t>Stripe Webhook 처리</t>
+          <t>LemonSqueezy Webhook 처리</t>
         </is>
       </c>
       <c r="E77" s="22" t="inlineStr">
@@ -4348,7 +4348,7 @@
       </c>
       <c r="I77" s="22" t="inlineStr">
         <is>
-          <t>app/api/billing/webhook/route.ts 6개 이벤트 처리</t>
+          <t>✅ app/api/billing/webhook/route.ts HMAC SHA-256 검증 + 6개 이벤트 처리</t>
         </is>
       </c>
     </row>
@@ -4360,7 +4360,7 @@
       </c>
       <c r="B78" s="22" t="inlineStr">
         <is>
-          <t>Stripe</t>
+          <t>LemonSqueezy</t>
         </is>
       </c>
       <c r="C78" s="23" t="inlineStr">
@@ -4370,7 +4370,7 @@
       </c>
       <c r="D78" s="28" t="inlineStr">
         <is>
-          <t>구독 상태 관리 (trialing→active→past_due→canceled)</t>
+          <t>구독 상태 관리 (on_trial→active→past_due→cancelled)</t>
         </is>
       </c>
       <c r="E78" s="22" t="inlineStr">
@@ -4395,7 +4395,7 @@
       </c>
       <c r="I78" s="22" t="inlineStr">
         <is>
-          <t>app/lib/billing/subscription.ts 라이프사이클 관리</t>
+          <t>✅ app/lib/billing/subscription.ts LemonSqueezy 상태 매핑 + DB billing_* 컬럼</t>
         </is>
       </c>
     </row>
@@ -4407,7 +4407,7 @@
       </c>
       <c r="B79" s="22" t="inlineStr">
         <is>
-          <t>Stripe</t>
+          <t>LemonSqueezy</t>
         </is>
       </c>
       <c r="C79" s="23" t="inlineStr">
@@ -4417,7 +4417,7 @@
       </c>
       <c r="D79" s="28" t="inlineStr">
         <is>
-          <t>인보이스 자동 발행</t>
+          <t>인보이스 자동 발행 (LemonSqueezy MoR 처리)</t>
         </is>
       </c>
       <c r="E79" s="22" t="inlineStr">
@@ -4427,7 +4427,7 @@
       </c>
       <c r="F79" s="30" t="inlineStr">
         <is>
-          <t>TODO</t>
+          <t>✅ Done</t>
         </is>
       </c>
       <c r="G79" s="29" t="inlineStr">
@@ -4442,7 +4442,7 @@
       </c>
       <c r="I79" s="22" t="inlineStr">
         <is>
-          <t>Stripe 자동 처리, 이메일 설정만</t>
+          <t>LemonSqueezy가 MoR로 인보이스/세금 자동 처리. 별도 설정 불필요</t>
         </is>
       </c>
     </row>
@@ -4630,7 +4630,7 @@
       </c>
       <c r="I83" s="22" t="inlineStr">
         <is>
-          <t>Stripe Customer Portal 연동 완료</t>
+          <t>✅ LemonSqueezy Customer Portal 연동 완료. subscription.urls.customer_portal</t>
         </is>
       </c>
     </row>
@@ -5462,10 +5462,10 @@
         <v>11</v>
       </c>
       <c r="C6" s="23" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D6" s="23" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E6" s="23" t="inlineStr">
         <is>

--- a/POTAL_B2B_Checklist.xlsx
+++ b/POTAL_B2B_Checklist.xlsx
@@ -2691,12 +2691,12 @@
       </c>
       <c r="E42" s="22" t="inlineStr">
         <is>
-          <t>tests/api-v1.test.ts</t>
+          <t>__tests__/api/api-v1-integration.test.ts</t>
         </is>
       </c>
       <c r="F42" s="30" t="inlineStr">
         <is>
-          <t>TODO</t>
+          <t>✅ Done</t>
         </is>
       </c>
       <c r="G42" s="25" t="inlineStr">
@@ -2711,7 +2711,7 @@
       </c>
       <c r="I42" s="28" t="inlineStr">
         <is>
-          <t>인증, rate limit, 정상 응답, 에러 응답</t>
+          <t>✅ 세션 26: 9 describe, 49 tests. 인증/rate limit/응답포맷/TLC계산/countries/edge cases</t>
         </is>
       </c>
     </row>
@@ -3863,7 +3863,7 @@
       </c>
       <c r="F67" s="30" t="inlineStr">
         <is>
-          <t>TODO</t>
+          <t>✅ Done</t>
         </is>
       </c>
       <c r="G67" s="29" t="inlineStr">
@@ -3878,7 +3878,7 @@
       </c>
       <c r="I67" s="22" t="inlineStr">
         <is>
-          <t>widget_configs 테이블의 theme JSON 적용</t>
+          <t>✅ 세션 26: widget_configs theme 자동 적용. primaryColor/borderRadius/fontFamily. data-* attrs + PotalWidget.init() 지원</t>
         </is>
       </c>
     </row>
@@ -3952,12 +3952,12 @@
       </c>
       <c r="E69" s="22" t="inlineStr">
         <is>
-          <t>app/seller/signup/page.tsx</t>
+          <t>app/auth/signup/page.tsx</t>
         </is>
       </c>
       <c r="F69" s="30" t="inlineStr">
         <is>
-          <t>TODO</t>
+          <t>✅ Done</t>
         </is>
       </c>
       <c r="G69" s="25" t="inlineStr">
@@ -3972,7 +3972,7 @@
       </c>
       <c r="I69" s="28" t="inlineStr">
         <is>
-          <t>회사명, 이메일, 웹사이트, 플랫폼 선택</t>
+          <t>✅ 세션 26: 기존 signup에 website/platform 필드 추가. register API 수정. DB migration 006</t>
         </is>
       </c>
     </row>
@@ -4093,12 +4093,12 @@
       </c>
       <c r="E72" s="22" t="inlineStr">
         <is>
-          <t>app/seller/guide/page.tsx</t>
+          <t>app/developers/quickstart/page.tsx</t>
         </is>
       </c>
       <c r="F72" s="30" t="inlineStr">
         <is>
-          <t>TODO</t>
+          <t>✅ Done</t>
         </is>
       </c>
       <c r="G72" s="25" t="inlineStr">
@@ -4113,7 +4113,7 @@
       </c>
       <c r="I72" s="22" t="inlineStr">
         <is>
-          <t>Shopify / WooCommerce / Custom 각각</t>
+          <t>✅ 세션 26: 3탭 Quick Start (Shopify 1분/JS Widget 2분/REST API 3분). CopyButton 포함</t>
         </is>
       </c>
     </row>
@@ -4516,12 +4516,12 @@
       </c>
       <c r="E81" s="22" t="inlineStr">
         <is>
-          <t>app/seller/dashboard/countries/page.tsx</t>
+          <t>app/dashboard/DashboardContent.tsx (Countries 탭)</t>
         </is>
       </c>
       <c r="F81" s="30" t="inlineStr">
         <is>
-          <t>TODO</t>
+          <t>✅ Done</t>
         </is>
       </c>
       <c r="G81" s="29" t="inlineStr">
@@ -4536,7 +4536,7 @@
       </c>
       <c r="I81" s="28" t="inlineStr">
         <is>
-          <t>어느 나라에서 가장 많이 조회하는지</t>
+          <t>✅ 세션 26: dashboard Countries 탭. /api/v1/sellers/analytics?type=countries API. 요청수/성공률/속도/분포 바</t>
         </is>
       </c>
     </row>
@@ -4563,12 +4563,12 @@
       </c>
       <c r="E82" s="22" t="inlineStr">
         <is>
-          <t>app/seller/dashboard/ai-platforms/page.tsx</t>
+          <t>app/dashboard/DashboardContent.tsx (Platforms 탭)</t>
         </is>
       </c>
       <c r="F82" s="30" t="inlineStr">
         <is>
-          <t>TODO</t>
+          <t>✅ Done</t>
         </is>
       </c>
       <c r="G82" s="29" t="inlineStr">
@@ -4583,7 +4583,7 @@
       </c>
       <c r="I82" s="22" t="inlineStr">
         <is>
-          <t>ChatGPT에서 몇 건, Gemini에서 몇 건</t>
+          <t>✅ 세션 26: dashboard Platforms 탭. /api/v1/sellers/analytics?type=platforms API. 엔드포인트별 카드 UI</t>
         </is>
       </c>
     </row>
@@ -4657,12 +4657,12 @@
       </c>
       <c r="E84" s="22" t="inlineStr">
         <is>
-          <t>app/seller/dashboard/logs/page.tsx</t>
+          <t>app/dashboard/DashboardContent.tsx (Logs 탭)</t>
         </is>
       </c>
       <c r="F84" s="30" t="inlineStr">
         <is>
-          <t>TODO</t>
+          <t>✅ Done</t>
         </is>
       </c>
       <c r="G84" s="31" t="inlineStr">
@@ -4677,7 +4677,7 @@
       </c>
       <c r="I84" s="28" t="inlineStr">
         <is>
-          <t>최근 100건 로그 테이블</t>
+          <t>✅ 세션 26: dashboard Logs 탭. /api/v1/sellers/analytics?type=logs API. 최근 100건 테이블</t>
         </is>
       </c>
     </row>
@@ -5399,10 +5399,10 @@
         <v>38</v>
       </c>
       <c r="C3" s="23" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D3" s="23" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E3" s="23" t="inlineStr">
         <is>
@@ -5441,10 +5441,10 @@
         <v>14</v>
       </c>
       <c r="C5" s="23" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="D5" s="23" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E5" s="23" t="inlineStr">
         <is>
@@ -5462,10 +5462,10 @@
         <v>11</v>
       </c>
       <c r="C6" s="23" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="D6" s="23" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="E6" s="23" t="inlineStr">
         <is>

--- a/POTAL_B2B_Checklist.xlsx
+++ b/POTAL_B2B_Checklist.xlsx
@@ -22,7 +22,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="16">
+  <fonts count="22">
     <font>
       <name val="Calibri"/>
       <charset val="1"/>
@@ -122,8 +122,32 @@
     <font>
       <color rgb="009C6500"/>
     </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <color rgb="00006400"/>
+    </font>
+    <font>
+      <color rgb="00CC0000"/>
+    </font>
+    <font>
+      <color rgb="00FF8C00"/>
+    </font>
   </fonts>
-  <fills count="13">
+  <fills count="15">
     <fill>
       <patternFill/>
     </fill>
@@ -194,8 +218,18 @@
         <fgColor rgb="00FFEB9C"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="0002122C"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FEF3C7"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="2">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -218,6 +252,20 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="00E5E7EB"/>
+      </left>
+      <right style="thin">
+        <color rgb="00E5E7EB"/>
+      </right>
+      <top style="thin">
+        <color rgb="00E5E7EB"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00E5E7EB"/>
+      </bottom>
+    </border>
   </borders>
   <cellStyleXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1">
@@ -229,7 +277,7 @@
     <xf numFmtId="42" fontId="3" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="3" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="39">
+  <cellXfs count="53">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="general" vertical="bottom"/>
     </xf>
@@ -345,6 +393,36 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="16" fillId="13" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="17" fillId="14" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="14" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="general" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="general" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="6">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -727,7 +805,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:I98"/>
+  <dimension ref="A1:I145"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="1" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="12" customWidth="1" style="18" min="1" max="1"/>
@@ -4709,7 +4787,7 @@
       </c>
       <c r="F85" s="30" t="inlineStr">
         <is>
-          <t>TODO</t>
+          <t>✅ Done</t>
         </is>
       </c>
       <c r="G85" s="25" t="inlineStr">
@@ -4724,7 +4802,7 @@
       </c>
       <c r="I85" s="22" t="inlineStr">
         <is>
-          <t>Chapter 1~97, 5,000+ 6자리 코드</t>
+          <t>세션 29: WCO HS 2022 전체 6자리 5,371 코드 + WITS+WTO 1,027,674건 186개국 MFN 관세율 벌크 수집 완료</t>
         </is>
       </c>
     </row>
@@ -4756,7 +4834,7 @@
       </c>
       <c r="F86" s="30" t="inlineStr">
         <is>
-          <t>TODO</t>
+          <t>⚠️ 전략변경</t>
         </is>
       </c>
       <c r="G86" s="29" t="inlineStr">
@@ -4771,7 +4849,7 @@
       </c>
       <c r="I86" s="28" t="inlineStr">
         <is>
-          <t>셀러 피드백 루프 활용</t>
+          <t>세션 30: AI 분류 6종 테스트 완료 (최대 60%). 모델 HS 지식 한계 → 대량 상품명 수집+룩업 전략으로 전환</t>
         </is>
       </c>
     </row>
@@ -4893,7 +4971,7 @@
       </c>
       <c r="F89" s="30" t="inlineStr">
         <is>
-          <t>TODO</t>
+          <t>✅ Done</t>
         </is>
       </c>
       <c r="G89" s="29" t="inlineStr">
@@ -4908,7 +4986,7 @@
       </c>
       <c r="I89" s="22" t="inlineStr">
         <is>
-          <t>country-data.ts에 181개국 포함. TH/VN/PH/ID/MY/SG 모두 세율 데이터 있음</t>
+          <t>세션 29: WITS+WTO 데이터에 ASEAN 전체 포함 (TH/VN/PH/ID/MY/SG)</t>
         </is>
       </c>
     </row>
@@ -4940,7 +5018,7 @@
       </c>
       <c r="F90" s="30" t="inlineStr">
         <is>
-          <t>TODO</t>
+          <t>✅ Done</t>
         </is>
       </c>
       <c r="G90" s="31" t="inlineStr">
@@ -4953,7 +5031,11 @@
           <t>3h</t>
         </is>
       </c>
-      <c r="I90" s="22" t="n"/>
+      <c r="I90" s="22" t="inlineStr">
+        <is>
+          <t>세션 29: GCC 6개국 WITS+WTO MFN 데이터 포함 (SA/AE/KW/QA/BH/OM)</t>
+        </is>
+      </c>
     </row>
     <row r="91" ht="15" customHeight="1" s="19">
       <c r="A91" s="36" t="inlineStr">
@@ -4983,7 +5065,7 @@
       </c>
       <c r="F91" s="30" t="inlineStr">
         <is>
-          <t>TODO</t>
+          <t>✅ Done</t>
         </is>
       </c>
       <c r="G91" s="31" t="inlineStr">
@@ -4998,7 +5080,7 @@
       </c>
       <c r="I91" s="22" t="inlineStr">
         <is>
-          <t>country-data.ts에 181개국 포함. BR/MX/AR/CL/CO 모두 세율 데이터 있음. Brazil ICMS/IPI 구현됨</t>
+          <t>세션 29: 남미 주요국 WITS+WTO MFN 데이터 포함 (BR/MX/AR/CL/CO)</t>
         </is>
       </c>
     </row>
@@ -5030,7 +5112,7 @@
       </c>
       <c r="F92" s="30" t="inlineStr">
         <is>
-          <t>TODO</t>
+          <t>✅ Done</t>
         </is>
       </c>
       <c r="G92" s="31" t="inlineStr">
@@ -5045,7 +5127,7 @@
       </c>
       <c r="I92" s="22" t="inlineStr">
         <is>
-          <t>country-data.ts에 181개국 포함. ZA/NG/KE/EG 모두 세율 데이터 있음</t>
+          <t>세션 29: 아프리카 주요국 WITS+WTO MFN 데이터 포함 (ZA/NG/KE/EG)</t>
         </is>
       </c>
     </row>
@@ -5227,7 +5309,11 @@
           <t>3h</t>
         </is>
       </c>
-      <c r="I96" s="22" t="n"/>
+      <c r="I96" s="22" t="inlineStr">
+        <is>
+          <t>세션 33: 기초 데이터 임포트 완료. 자동 업데이트 파이프라인은 추후</t>
+        </is>
+      </c>
     </row>
     <row r="97" ht="15" customHeight="1" s="19">
       <c r="A97" s="36" t="inlineStr">
@@ -5316,6 +5402,2092 @@
       <c r="I98" s="22" t="inlineStr">
         <is>
           <t>npm install @potal/sdk</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="44" t="inlineStr">
+        <is>
+          <t>Phase 5</t>
+        </is>
+      </c>
+      <c r="B99" s="45" t="inlineStr">
+        <is>
+          <t>HS Code DB 전략</t>
+        </is>
+      </c>
+      <c r="C99" s="46" t="inlineStr">
+        <is>
+          <t>5-15</t>
+        </is>
+      </c>
+      <c r="D99" s="45" t="inlineStr">
+        <is>
+          <t>AI HS Code 분류 테스트 6종 (Enrichment + HS-Aware)</t>
+        </is>
+      </c>
+      <c r="E99" s="45" t="inlineStr">
+        <is>
+          <t>test_enrichment_pipeline.py, test_enrichment_v2.py</t>
+        </is>
+      </c>
+      <c r="F99" s="47" t="inlineStr">
+        <is>
+          <t>✅ Done</t>
+        </is>
+      </c>
+      <c r="G99" s="48" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="H99" s="46" t="inlineStr">
+        <is>
+          <t>3h</t>
+        </is>
+      </c>
+      <c r="I99" s="49" t="inlineStr">
+        <is>
+          <t>세션 30: Raw 70B 50%/80%/90%, Enrichment 오히려 하락, CoT 20%. AI 한계 확인 → 전략 전환</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="44" t="inlineStr">
+        <is>
+          <t>Phase 5</t>
+        </is>
+      </c>
+      <c r="B100" s="45" t="inlineStr">
+        <is>
+          <t>HS Code DB 전략</t>
+        </is>
+      </c>
+      <c r="C100" s="46" t="inlineStr">
+        <is>
+          <t>5-16</t>
+        </is>
+      </c>
+      <c r="D100" s="45" t="inlineStr">
+        <is>
+          <t>4단계 전략 확정 (HS확보→자동업뎃→상품명DB→매핑)</t>
+        </is>
+      </c>
+      <c r="E100" s="45" t="inlineStr">
+        <is>
+          <t>session-context.md</t>
+        </is>
+      </c>
+      <c r="F100" s="47" t="inlineStr">
+        <is>
+          <t>✅ Done</t>
+        </is>
+      </c>
+      <c r="G100" s="48" t="inlineStr">
+        <is>
+          <t>Critical</t>
+        </is>
+      </c>
+      <c r="H100" s="46" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="I100" s="49" t="inlineStr">
+        <is>
+          <t>세션 30: Avalara 방식 벤치마킹. 50-80억 상품명 수집 + 50-80만 HS코드 매핑</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="44" t="inlineStr">
+        <is>
+          <t>Phase 5</t>
+        </is>
+      </c>
+      <c r="B101" s="45" t="inlineStr">
+        <is>
+          <t>HS Code DB 전략</t>
+        </is>
+      </c>
+      <c r="C101" s="46" t="inlineStr">
+        <is>
+          <t>5-17</t>
+        </is>
+      </c>
+      <c r="D101" s="45" t="inlineStr">
+        <is>
+          <t>WDC 5.95억 상품 데이터 파이프라인 구축</t>
+        </is>
+      </c>
+      <c r="E101" s="45" t="inlineStr">
+        <is>
+          <t>scripts/download_wdc_products.sh, scripts/extract_products_detailed.py</t>
+        </is>
+      </c>
+      <c r="F101" s="47" t="inlineStr">
+        <is>
+          <t>🔄 진행중</t>
+        </is>
+      </c>
+      <c r="G101" s="48" t="inlineStr">
+        <is>
+          <t>Critical</t>
+        </is>
+      </c>
+      <c r="H101" s="46" t="inlineStr">
+        <is>
+          <t>4h</t>
+        </is>
+      </c>
+      <c r="I101" s="49" t="inlineStr">
+        <is>
+          <t>세션 30→31: user-data 미실행→수동 download_wdc_v2.sh 실행. 179파일(257GB) 다운로드 진행 중 (nohup). EC2 Instance: i-0c114c6176439b9cb</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="44" t="inlineStr">
+        <is>
+          <t>Phase 5</t>
+        </is>
+      </c>
+      <c r="B102" s="45" t="inlineStr">
+        <is>
+          <t>HS Code DB 전략</t>
+        </is>
+      </c>
+      <c r="C102" s="46" t="inlineStr">
+        <is>
+          <t>5-18</t>
+        </is>
+      </c>
+      <c r="D102" s="45" t="inlineStr">
+        <is>
+          <t>AWS EC2 + S3 인프라 구축 (WDC 처리용)</t>
+        </is>
+      </c>
+      <c r="E102" s="45" t="inlineStr">
+        <is>
+          <t>AWS Console (920263653804, us-east-1)</t>
+        </is>
+      </c>
+      <c r="F102" s="47" t="inlineStr">
+        <is>
+          <t>✅ Done</t>
+        </is>
+      </c>
+      <c r="G102" s="48" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="H102" s="46" t="inlineStr">
+        <is>
+          <t>2h</t>
+        </is>
+      </c>
+      <c r="I102" s="49" t="inlineStr">
+        <is>
+          <t>세션 30: S3 potal-wdc-920263653804, EC2 i-0c114c6176439b9cb (m7i-flex.large), IAM potal-ec2-role</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" s="18" t="inlineStr">
+        <is>
+          <t>Phase 5</t>
+        </is>
+      </c>
+      <c r="B103" s="18" t="inlineStr">
+        <is>
+          <t>HS Code DB 전략</t>
+        </is>
+      </c>
+      <c r="C103" s="18" t="inlineStr">
+        <is>
+          <t>5-19</t>
+        </is>
+      </c>
+      <c r="D103" s="18" t="inlineStr">
+        <is>
+          <t>EC2 WDC 다운로드 문제 진단+수정 (user-data 미실행)</t>
+        </is>
+      </c>
+      <c r="E103" s="18" t="inlineStr">
+        <is>
+          <t>EC2 (i-0c114c6176439b9cb)</t>
+        </is>
+      </c>
+      <c r="F103" s="50" t="inlineStr">
+        <is>
+          <t>✅ Done</t>
+        </is>
+      </c>
+      <c r="G103" s="18" t="inlineStr">
+        <is>
+          <t>Critical</t>
+        </is>
+      </c>
+      <c r="H103" s="18" t="inlineStr">
+        <is>
+          <t>2h</t>
+        </is>
+      </c>
+      <c r="I103" s="18" t="inlineStr">
+        <is>
+          <t>세션 31: SSH 접속(SG port22 추가), cloud-init 미실행 확인, download_wdc_v2.sh 수동 생성+실행</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" s="18" t="inlineStr">
+        <is>
+          <t>Phase 5</t>
+        </is>
+      </c>
+      <c r="B104" s="18" t="inlineStr">
+        <is>
+          <t>HS Code DB 전략</t>
+        </is>
+      </c>
+      <c r="C104" s="18" t="inlineStr">
+        <is>
+          <t>5-20</t>
+        </is>
+      </c>
+      <c r="D104" s="18" t="inlineStr">
+        <is>
+          <t>WITS API 자동 관세 수집 시도 (실패)</t>
+        </is>
+      </c>
+      <c r="E104" s="18" t="inlineStr">
+        <is>
+          <t>EC2 download_tariff.sh</t>
+        </is>
+      </c>
+      <c r="F104" s="51" t="inlineStr">
+        <is>
+          <t>❌ Failed</t>
+        </is>
+      </c>
+      <c r="G104" s="18" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="H104" s="18" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="I104" s="18" t="inlineStr">
+        <is>
+          <t>세션 31: 50개국 전부 FAILED (API 스크립트 접근 차단)</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" s="18" t="inlineStr">
+        <is>
+          <t>Phase 5</t>
+        </is>
+      </c>
+      <c r="B105" s="18" t="inlineStr">
+        <is>
+          <t>HS Code DB 전략</t>
+        </is>
+      </c>
+      <c r="C105" s="18" t="inlineStr">
+        <is>
+          <t>5-21</t>
+        </is>
+      </c>
+      <c r="D105" s="18" t="inlineStr">
+        <is>
+          <t>정부 직접 다운로드 시도 (실패)</t>
+        </is>
+      </c>
+      <c r="E105" s="18" t="inlineStr">
+        <is>
+          <t>EC2 download_tariff_v2.sh</t>
+        </is>
+      </c>
+      <c r="F105" s="51" t="inlineStr">
+        <is>
+          <t>❌ Failed</t>
+        </is>
+      </c>
+      <c r="G105" s="18" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="H105" s="18" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="I105" s="18" t="inlineStr">
+        <is>
+          <t>세션 31: US HTS/EU TARIC/UK 등 대부분 0바이트 (wget 차단)</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" s="18" t="inlineStr">
+        <is>
+          <t>Phase 5</t>
+        </is>
+      </c>
+      <c r="B106" s="18" t="inlineStr">
+        <is>
+          <t>관세 데이터</t>
+        </is>
+      </c>
+      <c r="C106" s="18" t="inlineStr">
+        <is>
+          <t>5-22</t>
+        </is>
+      </c>
+      <c r="D106" s="18" t="inlineStr">
+        <is>
+          <t>ITC MacMap MFN 관세율 53개국 수동 벌크 다운로드</t>
+        </is>
+      </c>
+      <c r="E106" s="18" t="inlineStr">
+        <is>
+          <t>data/itc_macmap/by_country/</t>
+        </is>
+      </c>
+      <c r="F106" s="50" t="inlineStr">
+        <is>
+          <t>✅ Done</t>
+        </is>
+      </c>
+      <c r="G106" s="18" t="inlineStr">
+        <is>
+          <t>Critical</t>
+        </is>
+      </c>
+      <c r="H106" s="18" t="inlineStr">
+        <is>
+          <t>4h</t>
+        </is>
+      </c>
+      <c r="I106" s="18" t="inlineStr">
+        <is>
+          <t>세션 31: 53개국 73파일 721,582건 191MB. NTLC 8-12자리. 주요 교역국 전체 커버</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" s="18" t="inlineStr">
+        <is>
+          <t>Phase 5</t>
+        </is>
+      </c>
+      <c r="B107" s="18" t="inlineStr">
+        <is>
+          <t>관세 데이터</t>
+        </is>
+      </c>
+      <c r="C107" s="18" t="inlineStr">
+        <is>
+          <t>5-23</t>
+        </is>
+      </c>
+      <c r="D107" s="18" t="inlineStr">
+        <is>
+          <t>MacMap 데이터 파일 정리 (by_country 구조화)</t>
+        </is>
+      </c>
+      <c r="E107" s="18" t="inlineStr">
+        <is>
+          <t>data/itc_macmap/by_country/{ISO3}/</t>
+        </is>
+      </c>
+      <c r="F107" s="50" t="inlineStr">
+        <is>
+          <t>✅ Done</t>
+        </is>
+      </c>
+      <c r="G107" s="18" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="H107" s="18" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="I107" s="18" t="inlineStr">
+        <is>
+          <t>세션 31: BulkDownloadResult×4 + zip×6 + 중복파일 삭제. 53개국 폴더 정리</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" s="18" t="inlineStr">
+        <is>
+          <t>Phase 5</t>
+        </is>
+      </c>
+      <c r="B108" s="18" t="inlineStr">
+        <is>
+          <t>관세 데이터</t>
+        </is>
+      </c>
+      <c r="C108" s="18" t="inlineStr">
+        <is>
+          <t>5-24</t>
+        </is>
+      </c>
+      <c r="D108" s="18" t="inlineStr">
+        <is>
+          <t>TTBD 반덤핑/상계관세/세이프가드 데이터 수집 + Supabase 임포트</t>
+        </is>
+      </c>
+      <c r="E108" s="18" t="inlineStr">
+        <is>
+          <t>data/itc_macmap/</t>
+        </is>
+      </c>
+      <c r="F108" s="52" t="inlineStr">
+        <is>
+          <t>✅ Done</t>
+        </is>
+      </c>
+      <c r="G108" s="18" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="H108" s="18" t="inlineStr">
+        <is>
+          <t>4h</t>
+        </is>
+      </c>
+      <c r="I108" s="18" t="inlineStr">
+        <is>
+          <t>세션 33: TTBD 36개국 AD + 19개국 CVD + WTO SG → 4개 테이블 119,706행</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" s="18" t="inlineStr">
+        <is>
+          <t>Phase 5</t>
+        </is>
+      </c>
+      <c r="B109" s="18" t="inlineStr">
+        <is>
+          <t>관세 데이터</t>
+        </is>
+      </c>
+      <c r="C109" s="18" t="inlineStr">
+        <is>
+          <t>5-25</t>
+        </is>
+      </c>
+      <c r="D109" s="18" t="inlineStr">
+        <is>
+          <t>MacMap NTLC 데이터 Supabase import</t>
+        </is>
+      </c>
+      <c r="E109" s="18" t="inlineStr">
+        <is>
+          <t>supabase/migrations/</t>
+        </is>
+      </c>
+      <c r="F109" s="52" t="inlineStr">
+        <is>
+          <t>✅ Done</t>
+        </is>
+      </c>
+      <c r="G109" s="18" t="inlineStr">
+        <is>
+          <t>Critical</t>
+        </is>
+      </c>
+      <c r="H109" s="18" t="inlineStr">
+        <is>
+          <t>3h</t>
+        </is>
+      </c>
+      <c r="I109" s="18" t="inlineStr">
+        <is>
+          <t>세션 32: macmap_ntlc_rates 537,894행 53개국 완료. Management API로 54블록 임포트 (5개 413에러→10분할 재시도 전체 성공)</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" s="44" t="inlineStr">
+        <is>
+          <t>Phase 5</t>
+        </is>
+      </c>
+      <c r="B110" s="45" t="inlineStr">
+        <is>
+          <t>HS Code DB 전략</t>
+        </is>
+      </c>
+      <c r="C110" s="46" t="inlineStr">
+        <is>
+          <t>5-19</t>
+        </is>
+      </c>
+      <c r="D110" s="45" t="inlineStr">
+        <is>
+          <t>Google Taxonomy 5,596 카테고리 다운로드</t>
+        </is>
+      </c>
+      <c r="E110" s="45" t="inlineStr">
+        <is>
+          <t>product-data/google_taxonomy.txt</t>
+        </is>
+      </c>
+      <c r="F110" s="47" t="inlineStr">
+        <is>
+          <t>✅ Done</t>
+        </is>
+      </c>
+      <c r="G110" s="48" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="H110" s="46" t="inlineStr">
+        <is>
+          <t>0.5h</t>
+        </is>
+      </c>
+      <c r="I110" s="49" t="inlineStr">
+        <is>
+          <t>세션 30: Google Product Taxonomy en-US 전체 다운로드 완료</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" s="44" t="inlineStr">
+        <is>
+          <t>Phase 5</t>
+        </is>
+      </c>
+      <c r="B111" s="45" t="inlineStr">
+        <is>
+          <t>HS Code DB 전략</t>
+        </is>
+      </c>
+      <c r="C111" s="46" t="inlineStr">
+        <is>
+          <t>5-20</t>
+        </is>
+      </c>
+      <c r="D111" s="45" t="inlineStr">
+        <is>
+          <t>Stanford Amazon 9.4M + MAVE 2.2M 추가 데이터 병합</t>
+        </is>
+      </c>
+      <c r="E111" s="45" t="inlineStr">
+        <is>
+          <t>data/</t>
+        </is>
+      </c>
+      <c r="F111" s="47" t="inlineStr">
+        <is>
+          <t>TODO</t>
+        </is>
+      </c>
+      <c r="G111" s="48" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="H111" s="46" t="inlineStr">
+        <is>
+          <t>2h</t>
+        </is>
+      </c>
+      <c r="I111" s="49" t="inlineStr">
+        <is>
+          <t>WDC 완료 후 추가 데이터소스 병합. Stanford 메타데이터 + MAVE 속성(material 등)</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" s="44" t="inlineStr">
+        <is>
+          <t>Phase 5</t>
+        </is>
+      </c>
+      <c r="B112" s="45" t="inlineStr">
+        <is>
+          <t>HS Code DB 전략</t>
+        </is>
+      </c>
+      <c r="C112" s="46" t="inlineStr">
+        <is>
+          <t>5-21</t>
+        </is>
+      </c>
+      <c r="D112" s="45" t="inlineStr">
+        <is>
+          <t>상품명 → HS 코드 매핑 파이프라인 설계</t>
+        </is>
+      </c>
+      <c r="E112" s="45" t="inlineStr">
+        <is>
+          <t>app/lib/cost-engine/product-mapper/</t>
+        </is>
+      </c>
+      <c r="F112" s="47" t="inlineStr">
+        <is>
+          <t>TODO</t>
+        </is>
+      </c>
+      <c r="G112" s="48" t="inlineStr">
+        <is>
+          <t>Critical</t>
+        </is>
+      </c>
+      <c r="H112" s="46" t="inlineStr">
+        <is>
+          <t>4h</t>
+        </is>
+      </c>
+      <c r="I112" s="49" t="inlineStr">
+        <is>
+          <t>세관 공개데이터(정답) + 이커머스 카테고리 매핑 + AI 배치 분류 3단계</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" s="44" t="inlineStr">
+        <is>
+          <t>Phase 5</t>
+        </is>
+      </c>
+      <c r="B113" s="45" t="inlineStr">
+        <is>
+          <t>HS Code DB 전략</t>
+        </is>
+      </c>
+      <c r="C113" s="46" t="inlineStr">
+        <is>
+          <t>5-22</t>
+        </is>
+      </c>
+      <c r="D113" s="45" t="inlineStr">
+        <is>
+          <t>국가별 8-12자리 HS 코드 확장 (50개국 관세청)</t>
+        </is>
+      </c>
+      <c r="E113" s="45" t="inlineStr">
+        <is>
+          <t>app/lib/cost-engine/hs-code/</t>
+        </is>
+      </c>
+      <c r="F113" s="47" t="inlineStr">
+        <is>
+          <t>TODO</t>
+        </is>
+      </c>
+      <c r="G113" s="48" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="H113" s="46" t="inlineStr">
+        <is>
+          <t>6h</t>
+        </is>
+      </c>
+      <c r="I113" s="49" t="inlineStr">
+        <is>
+          <t>6자리→8-12자리 확장. 미국 HTS 10자리, EU TARIC 10자리, 한국 HSK 10자리 등</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" s="18" t="inlineStr">
+        <is>
+          <t>Phase 5</t>
+        </is>
+      </c>
+      <c r="B114" s="18" t="inlineStr">
+        <is>
+          <t>관세 데이터</t>
+        </is>
+      </c>
+      <c r="C114" s="18" t="inlineStr">
+        <is>
+          <t>5-26</t>
+        </is>
+      </c>
+      <c r="D114" s="18" t="inlineStr">
+        <is>
+          <t>Supabase 마이그레이션 010-016 실행 (Management API)</t>
+        </is>
+      </c>
+      <c r="E114" s="18" t="inlineStr">
+        <is>
+          <t>supabase/migrations/</t>
+        </is>
+      </c>
+      <c r="F114" s="18" t="inlineStr">
+        <is>
+          <t>✅ Done</t>
+        </is>
+      </c>
+      <c r="G114" s="18" t="inlineStr">
+        <is>
+          <t>Critical</t>
+        </is>
+      </c>
+      <c r="H114" s="18" t="inlineStr">
+        <is>
+          <t>3h</t>
+        </is>
+      </c>
+      <c r="I114" s="18" t="inlineStr">
+        <is>
+          <t>세션 32: countries 240, vat_gst 240, de_minimis 240, customs_fees 240, trade_agreements 1,319행. 010 iso_code_3 6개 수정 (BQ→BES등)</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" s="18" t="inlineStr">
+        <is>
+          <t>Phase 5</t>
+        </is>
+      </c>
+      <c r="B115" s="18" t="inlineStr">
+        <is>
+          <t>관세 데이터</t>
+        </is>
+      </c>
+      <c r="C115" s="18" t="inlineStr">
+        <is>
+          <t>5-27</t>
+        </is>
+      </c>
+      <c r="D115" s="18" t="inlineStr">
+        <is>
+          <t>016_macmap_bulk_tables.sql DDL 생성</t>
+        </is>
+      </c>
+      <c r="E115" s="18" t="inlineStr">
+        <is>
+          <t>supabase/migrations/016_macmap_bulk_tables.sql</t>
+        </is>
+      </c>
+      <c r="F115" s="18" t="inlineStr">
+        <is>
+          <t>✅ Done</t>
+        </is>
+      </c>
+      <c r="G115" s="18" t="inlineStr">
+        <is>
+          <t>Critical</t>
+        </is>
+      </c>
+      <c r="H115" s="18" t="inlineStr">
+        <is>
+          <t>4h</t>
+        </is>
+      </c>
+      <c r="I115" s="18" t="inlineStr">
+        <is>
+          <t>세션 32: macmap_min_rates + macmap_agr_rates + macmap_trade_agreements 3테이블 + lookup_duty_rate_v2() 4단계 폴백 함수 + 1,319 무역협정</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" s="18" t="inlineStr">
+        <is>
+          <t>Phase 5</t>
+        </is>
+      </c>
+      <c r="B116" s="18" t="inlineStr">
+        <is>
+          <t>관세 데이터</t>
+        </is>
+      </c>
+      <c r="C116" s="18" t="inlineStr">
+        <is>
+          <t>5-28</t>
+        </is>
+      </c>
+      <c r="D116" s="18" t="inlineStr">
+        <is>
+          <t>M49→ISO2 완전 매핑 생성 (237+개국)</t>
+        </is>
+      </c>
+      <c r="E116" s="18" t="inlineStr">
+        <is>
+          <t>m49_to_iso2_full.py</t>
+        </is>
+      </c>
+      <c r="F116" s="18" t="inlineStr">
+        <is>
+          <t>✅ Done</t>
+        </is>
+      </c>
+      <c r="G116" s="18" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="H116" s="18" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="I116" s="18" t="inlineStr">
+        <is>
+          <t>세션 32: ITC 특수코드 포함 (490→TW, 699→IN, 757→CH, 918→EU, 842→US, 381→IT)</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="18" t="inlineStr">
+        <is>
+          <t>Phase 5</t>
+        </is>
+      </c>
+      <c r="B117" s="18" t="inlineStr">
+        <is>
+          <t>관세 데이터</t>
+        </is>
+      </c>
+      <c r="C117" s="18" t="inlineStr">
+        <is>
+          <t>5-29</t>
+        </is>
+      </c>
+      <c r="D117" s="18" t="inlineStr">
+        <is>
+          <t>MacMap MIN 벌크 임포트 (130M행)</t>
+        </is>
+      </c>
+      <c r="E117" s="18" t="inlineStr">
+        <is>
+          <t>import_min_via_api.py</t>
+        </is>
+      </c>
+      <c r="F117" s="18" t="inlineStr">
+        <is>
+          <t>🔄 진행중</t>
+        </is>
+      </c>
+      <c r="G117" s="18" t="inlineStr">
+        <is>
+          <t>Critical</t>
+        </is>
+      </c>
+      <c r="H117" s="18" t="inlineStr">
+        <is>
+          <t>5h</t>
+        </is>
+      </c>
+      <c r="I117" s="18" t="inlineStr">
+        <is>
+          <t>세션 33: ~5.4M/130M행 (AE+AR+AU 3개국 완료). 백그라운드 진행중</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="18" t="inlineStr">
+        <is>
+          <t>Phase 5</t>
+        </is>
+      </c>
+      <c r="B118" s="18" t="inlineStr">
+        <is>
+          <t>관세 데이터</t>
+        </is>
+      </c>
+      <c r="C118" s="18" t="inlineStr">
+        <is>
+          <t>5-30</t>
+        </is>
+      </c>
+      <c r="D118" s="18" t="inlineStr">
+        <is>
+          <t>MacMap AGR 벌크 임포트 (148M행)</t>
+        </is>
+      </c>
+      <c r="E118" s="18" t="inlineStr">
+        <is>
+          <t>import_min_via_api.py (수정)</t>
+        </is>
+      </c>
+      <c r="F118" s="18" t="inlineStr">
+        <is>
+          <t>TODO</t>
+        </is>
+      </c>
+      <c r="G118" s="18" t="inlineStr">
+        <is>
+          <t>Critical</t>
+        </is>
+      </c>
+      <c r="H118" s="18" t="inlineStr">
+        <is>
+          <t>6h</t>
+        </is>
+      </c>
+      <c r="I118" s="18" t="inlineStr">
+        <is>
+          <t>MIN 완료 후 진행. 148M행 + trade_agreement_id 매핑</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="18" t="inlineStr">
+        <is>
+          <t>Phase 5</t>
+        </is>
+      </c>
+      <c r="B119" s="18" t="inlineStr">
+        <is>
+          <t>관세 데이터</t>
+        </is>
+      </c>
+      <c r="C119" s="18" t="inlineStr">
+        <is>
+          <t>5-31</t>
+        </is>
+      </c>
+      <c r="D119" s="18" t="inlineStr">
+        <is>
+          <t>Management API 기반 데이터 파이프라인 구축</t>
+        </is>
+      </c>
+      <c r="E119" s="18" t="inlineStr">
+        <is>
+          <t>execute_migrations.py, import_min_via_api.py</t>
+        </is>
+      </c>
+      <c r="F119" s="18" t="inlineStr">
+        <is>
+          <t>✅ Done</t>
+        </is>
+      </c>
+      <c r="G119" s="18" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="H119" s="18" t="inlineStr">
+        <is>
+          <t>3h</t>
+        </is>
+      </c>
+      <c r="I119" s="18" t="inlineStr">
+        <is>
+          <t>세션 32: curl+Supabase Management API로 SQL 실행. BEGIN/COMMIT 블록 분할, 413에러 자동 분할, 진행 추적</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="18" t="inlineStr">
+        <is>
+          <t>Phase 5</t>
+        </is>
+      </c>
+      <c r="B120" s="18" t="inlineStr">
+        <is>
+          <t>관세 데이터</t>
+        </is>
+      </c>
+      <c r="C120" s="18" t="inlineStr">
+        <is>
+          <t>5-32</t>
+        </is>
+      </c>
+      <c r="D120" s="18" t="inlineStr">
+        <is>
+          <t>lookup_duty_rate_v2() 검증 + 통합 테스트</t>
+        </is>
+      </c>
+      <c r="E120" s="18" t="inlineStr">
+        <is>
+          <t>Supabase SQL</t>
+        </is>
+      </c>
+      <c r="F120" s="18" t="inlineStr">
+        <is>
+          <t>TODO</t>
+        </is>
+      </c>
+      <c r="G120" s="18" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="H120" s="18" t="inlineStr">
+        <is>
+          <t>2h</t>
+        </is>
+      </c>
+      <c r="I120" s="18" t="inlineStr">
+        <is>
+          <t>MIN+AGR 임포트 완료 후. 4단계 폴백 (exact MIN→prefix MIN→MFN NTLC→WITS HS6) 검증</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" s="39" t="inlineStr">
+        <is>
+          <t>Phase 6</t>
+        </is>
+      </c>
+      <c r="B122" s="39" t="n"/>
+      <c r="C122" s="39" t="n"/>
+      <c r="D122" s="39">
+        <f>== 33개 기능 업계 최고 달성 (세션 28 확정) ===</f>
+        <v/>
+      </c>
+      <c r="E122" s="39" t="n"/>
+      <c r="F122" s="39" t="n"/>
+      <c r="G122" s="39" t="n"/>
+      <c r="H122" s="39" t="n"/>
+      <c r="I122" s="39" t="n"/>
+    </row>
+    <row r="124">
+      <c r="A124" s="40" t="inlineStr">
+        <is>
+          <t>Phase 6</t>
+        </is>
+      </c>
+      <c r="B124" s="40" t="inlineStr">
+        <is>
+          <t>HS Code 강화</t>
+        </is>
+      </c>
+      <c r="C124" s="40" t="inlineStr">
+        <is>
+          <t>6-01</t>
+        </is>
+      </c>
+      <c r="D124" s="41" t="inlineStr">
+        <is>
+          <t>WCO/USITC/TARIC/HSK 공개 HS Code 대량 import (443→50만+)</t>
+        </is>
+      </c>
+      <c r="E124" s="41" t="inlineStr">
+        <is>
+          <t>app/lib/cost-engine/hs-code/</t>
+        </is>
+      </c>
+      <c r="F124" s="40" t="inlineStr">
+        <is>
+          <t>✅ Done</t>
+        </is>
+      </c>
+      <c r="G124" s="40" t="inlineStr">
+        <is>
+          <t>Critical</t>
+        </is>
+      </c>
+      <c r="H124" s="40" t="inlineStr">
+        <is>
+          <t>8h</t>
+        </is>
+      </c>
+      <c r="I124" s="41" t="inlineStr">
+        <is>
+          <t>세션 29: HS 5,371 + WITS+WTO 1,027,674건. 세션 30: WDC 5.95억 상품 파이프라인 시작 (AWS EC2 자동 실행 중)</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" s="40" t="inlineStr">
+        <is>
+          <t>Phase 6</t>
+        </is>
+      </c>
+      <c r="B125" s="40" t="inlineStr">
+        <is>
+          <t>HS Code 강화</t>
+        </is>
+      </c>
+      <c r="C125" s="40" t="inlineStr">
+        <is>
+          <t>6-02</t>
+        </is>
+      </c>
+      <c r="D125" s="41" t="inlineStr">
+        <is>
+          <t>이미지 기반 HS Code 분류 (GPT-4o-mini Vision)</t>
+        </is>
+      </c>
+      <c r="E125" s="41" t="inlineStr">
+        <is>
+          <t>app/lib/cost-engine/ai-classifier/</t>
+        </is>
+      </c>
+      <c r="F125" s="40" t="inlineStr">
+        <is>
+          <t>TODO</t>
+        </is>
+      </c>
+      <c r="G125" s="40" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="H125" s="40" t="inlineStr">
+        <is>
+          <t>4h</t>
+        </is>
+      </c>
+      <c r="I125" s="41" t="inlineStr">
+        <is>
+          <t>GPT-4o-mini 비전 API. 건당 $0.003. Zonos 대응</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" s="40" t="inlineStr">
+        <is>
+          <t>Phase 6</t>
+        </is>
+      </c>
+      <c r="B126" s="40" t="inlineStr">
+        <is>
+          <t>HS Code 강화</t>
+        </is>
+      </c>
+      <c r="C126" s="40" t="inlineStr">
+        <is>
+          <t>6-03</t>
+        </is>
+      </c>
+      <c r="D126" s="41" t="inlineStr">
+        <is>
+          <t>다국어 분류 50개+ 언어 확대</t>
+        </is>
+      </c>
+      <c r="E126" s="41" t="inlineStr">
+        <is>
+          <t>app/lib/cost-engine/ai-classifier/</t>
+        </is>
+      </c>
+      <c r="F126" s="40" t="inlineStr">
+        <is>
+          <t>TODO</t>
+        </is>
+      </c>
+      <c r="G126" s="40" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="H126" s="40" t="inlineStr">
+        <is>
+          <t>2h</t>
+        </is>
+      </c>
+      <c r="I126" s="41" t="inlineStr">
+        <is>
+          <t>AI 프롬프트 다국어 지시 추가. 비용 $0</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" s="40" t="inlineStr">
+        <is>
+          <t>Phase 6</t>
+        </is>
+      </c>
+      <c r="B127" s="40" t="inlineStr">
+        <is>
+          <t>핵심 계산</t>
+        </is>
+      </c>
+      <c r="C127" s="40" t="inlineStr">
+        <is>
+          <t>6-04</t>
+        </is>
+      </c>
+      <c r="D127" s="41" t="inlineStr">
+        <is>
+          <t>반덤핑/세이프가드 관세 DB 구축 + AI 적용</t>
+        </is>
+      </c>
+      <c r="E127" s="41" t="inlineStr">
+        <is>
+          <t>app/lib/cost-engine/special-duties/</t>
+        </is>
+      </c>
+      <c r="F127" s="40" t="inlineStr">
+        <is>
+          <t>TODO</t>
+        </is>
+      </c>
+      <c r="G127" s="40" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="H127" s="40" t="inlineStr">
+        <is>
+          <t>6h</t>
+        </is>
+      </c>
+      <c r="I127" s="41" t="inlineStr">
+        <is>
+          <t>세션 29: ITC MacMap 계정 에러 → ITC 문의 중 (marketanalysis@intracen.org). 응답 후 벌크 다운로드 예정</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" s="40" t="inlineStr">
+        <is>
+          <t>Phase 6</t>
+        </is>
+      </c>
+      <c r="B128" s="40" t="inlineStr">
+        <is>
+          <t>데이터 커버리지</t>
+        </is>
+      </c>
+      <c r="C128" s="40" t="inlineStr">
+        <is>
+          <t>6-05</t>
+        </is>
+      </c>
+      <c r="D128" s="41" t="inlineStr">
+        <is>
+          <t>관세율 DB 실시간 업데이트 7개국→20개국+ 확대</t>
+        </is>
+      </c>
+      <c r="E128" s="41" t="inlineStr">
+        <is>
+          <t>app/lib/cost-engine/tariff-api/</t>
+        </is>
+      </c>
+      <c r="F128" s="40" t="inlineStr">
+        <is>
+          <t>✅ Done</t>
+        </is>
+      </c>
+      <c r="G128" s="40" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="H128" s="40" t="inlineStr">
+        <is>
+          <t>8h</t>
+        </is>
+      </c>
+      <c r="I128" s="41" t="inlineStr">
+        <is>
+          <t>세션 29: 186개국 MFN DB 완료. 7개 정부 API + WITS+WTO 벌크. Make.com 정기 업데이트 자동화 필요</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" s="40" t="inlineStr">
+        <is>
+          <t>Phase 6</t>
+        </is>
+      </c>
+      <c r="B129" s="40" t="inlineStr">
+        <is>
+          <t>데이터 커버리지</t>
+        </is>
+      </c>
+      <c r="C129" s="40" t="inlineStr">
+        <is>
+          <t>6-06</t>
+        </is>
+      </c>
+      <c r="D129" s="41" t="inlineStr">
+        <is>
+          <t>다국어 응답 7개→20개+ 언어 확대</t>
+        </is>
+      </c>
+      <c r="E129" s="41" t="inlineStr">
+        <is>
+          <t>app/lib/cost-engine/country-i18n.ts</t>
+        </is>
+      </c>
+      <c r="F129" s="40" t="inlineStr">
+        <is>
+          <t>TODO</t>
+        </is>
+      </c>
+      <c r="G129" s="40" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="H129" s="40" t="inlineStr">
+        <is>
+          <t>3h</t>
+        </is>
+      </c>
+      <c r="I129" s="41" t="inlineStr">
+        <is>
+          <t>AI 번역 활용. 비용 미미</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" s="40" t="inlineStr">
+        <is>
+          <t>Phase 6</t>
+        </is>
+      </c>
+      <c r="B130" s="40" t="inlineStr">
+        <is>
+          <t>컴플라이언스</t>
+        </is>
+      </c>
+      <c r="C130" s="40" t="inlineStr">
+        <is>
+          <t>6-07</t>
+        </is>
+      </c>
+      <c r="D130" s="41" t="inlineStr">
+        <is>
+          <t>수출입 제한 물품 검사 DB + AI 판별</t>
+        </is>
+      </c>
+      <c r="E130" s="41" t="inlineStr">
+        <is>
+          <t>app/lib/cost-engine/compliance/</t>
+        </is>
+      </c>
+      <c r="F130" s="40" t="inlineStr">
+        <is>
+          <t>TODO</t>
+        </is>
+      </c>
+      <c r="G130" s="40" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="H130" s="40" t="inlineStr">
+        <is>
+          <t>6h</t>
+        </is>
+      </c>
+      <c r="I130" s="41" t="inlineStr">
+        <is>
+          <t>세션 29: WTO QR API 403 차단 (CloudFront). MacMap NTM 또는 대체 소스 필요. TFAD 137개국 통관절차 데이터 확보</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" s="40" t="inlineStr">
+        <is>
+          <t>Phase 6</t>
+        </is>
+      </c>
+      <c r="B131" s="40" t="inlineStr">
+        <is>
+          <t>컴플라이언스</t>
+        </is>
+      </c>
+      <c r="C131" s="40" t="inlineStr">
+        <is>
+          <t>6-08</t>
+        </is>
+      </c>
+      <c r="D131" s="41" t="inlineStr">
+        <is>
+          <t>통관서류 자동생성 (Commercial Invoice/Packing List)</t>
+        </is>
+      </c>
+      <c r="E131" s="41" t="inlineStr">
+        <is>
+          <t>app/lib/cost-engine/docs-generator/</t>
+        </is>
+      </c>
+      <c r="F131" s="40" t="inlineStr">
+        <is>
+          <t>TODO</t>
+        </is>
+      </c>
+      <c r="G131" s="40" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="H131" s="40" t="inlineStr">
+        <is>
+          <t>4h</t>
+        </is>
+      </c>
+      <c r="I131" s="41" t="inlineStr">
+        <is>
+          <t>AI로 서류 생성. TLC 결과 데이터 활용</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" s="40" t="inlineStr">
+        <is>
+          <t>Phase 6</t>
+        </is>
+      </c>
+      <c r="B132" s="40" t="inlineStr">
+        <is>
+          <t>체크아웃</t>
+        </is>
+      </c>
+      <c r="C132" s="40" t="inlineStr">
+        <is>
+          <t>6-09</t>
+        </is>
+      </c>
+      <c r="D132" s="41" t="inlineStr">
+        <is>
+          <t>DDP 체크아웃 통합 (Stripe 연동)</t>
+        </is>
+      </c>
+      <c r="E132" s="41" t="inlineStr">
+        <is>
+          <t>app/api/checkout/</t>
+        </is>
+      </c>
+      <c r="F132" s="40" t="inlineStr">
+        <is>
+          <t>TODO</t>
+        </is>
+      </c>
+      <c r="G132" s="40" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="H132" s="40" t="inlineStr">
+        <is>
+          <t>8h</t>
+        </is>
+      </c>
+      <c r="I132" s="41" t="inlineStr">
+        <is>
+          <t>Pro+ 전용. Stripe Payment Intent + TLC 통합</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" s="40" t="inlineStr">
+        <is>
+          <t>Phase 6</t>
+        </is>
+      </c>
+      <c r="B133" s="40" t="inlineStr">
+        <is>
+          <t>체크아웃</t>
+        </is>
+      </c>
+      <c r="C133" s="40" t="inlineStr">
+        <is>
+          <t>6-10</t>
+        </is>
+      </c>
+      <c r="D133" s="41" t="inlineStr">
+        <is>
+          <t>다중 통화 표시 (환율API 이미 있음)</t>
+        </is>
+      </c>
+      <c r="E133" s="41" t="inlineStr">
+        <is>
+          <t>app/lib/cost-engine/</t>
+        </is>
+      </c>
+      <c r="F133" s="40" t="inlineStr">
+        <is>
+          <t>TODO</t>
+        </is>
+      </c>
+      <c r="G133" s="40" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="H133" s="40" t="inlineStr">
+        <is>
+          <t>3h</t>
+        </is>
+      </c>
+      <c r="I133" s="41" t="inlineStr">
+        <is>
+          <t>프론트엔드 통화 변환 로직 추가</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" s="40" t="inlineStr">
+        <is>
+          <t>Phase 6</t>
+        </is>
+      </c>
+      <c r="B134" s="40" t="inlineStr">
+        <is>
+          <t>플랫폼 통합</t>
+        </is>
+      </c>
+      <c r="C134" s="40" t="inlineStr">
+        <is>
+          <t>6-11</t>
+        </is>
+      </c>
+      <c r="D134" s="41" t="inlineStr">
+        <is>
+          <t>WooCommerce 플러그인 개발</t>
+        </is>
+      </c>
+      <c r="E134" s="41" t="inlineStr">
+        <is>
+          <t>plugins/woocommerce/</t>
+        </is>
+      </c>
+      <c r="F134" s="40" t="inlineStr">
+        <is>
+          <t>TODO</t>
+        </is>
+      </c>
+      <c r="G134" s="40" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="H134" s="40" t="inlineStr">
+        <is>
+          <t>6h</t>
+        </is>
+      </c>
+      <c r="I134" s="41" t="inlineStr">
+        <is>
+          <t>WordPress 플러그인 형태. PHP</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" s="40" t="inlineStr">
+        <is>
+          <t>Phase 6</t>
+        </is>
+      </c>
+      <c r="B135" s="40" t="inlineStr">
+        <is>
+          <t>플랫폼 통합</t>
+        </is>
+      </c>
+      <c r="C135" s="40" t="inlineStr">
+        <is>
+          <t>6-12</t>
+        </is>
+      </c>
+      <c r="D135" s="41" t="inlineStr">
+        <is>
+          <t>BigCommerce/Magento 플러그인 (Pro+)</t>
+        </is>
+      </c>
+      <c r="E135" s="41" t="inlineStr">
+        <is>
+          <t>plugins/</t>
+        </is>
+      </c>
+      <c r="F135" s="40" t="inlineStr">
+        <is>
+          <t>TODO</t>
+        </is>
+      </c>
+      <c r="G135" s="40" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="H135" s="40" t="inlineStr">
+        <is>
+          <t>6h</t>
+        </is>
+      </c>
+      <c r="I135" s="41" t="inlineStr">
+        <is>
+          <t>Pro 이상 전용</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" s="40" t="inlineStr">
+        <is>
+          <t>Phase 6</t>
+        </is>
+      </c>
+      <c r="B136" s="40" t="inlineStr">
+        <is>
+          <t>자동화</t>
+        </is>
+      </c>
+      <c r="C136" s="40" t="inlineStr">
+        <is>
+          <t>6-13</t>
+        </is>
+      </c>
+      <c r="D136" s="41" t="inlineStr">
+        <is>
+          <t>원산지 자동 감지 (AI 프롬프트 추가)</t>
+        </is>
+      </c>
+      <c r="E136" s="41" t="inlineStr">
+        <is>
+          <t>app/lib/cost-engine/ai-classifier/</t>
+        </is>
+      </c>
+      <c r="F136" s="40" t="inlineStr">
+        <is>
+          <t>TODO</t>
+        </is>
+      </c>
+      <c r="G136" s="40" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="H136" s="40" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="I136" s="41" t="inlineStr">
+        <is>
+          <t>GPT 프롬프트에 원산지 추정 지시 추가. 비용 $0</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" s="40" t="inlineStr">
+        <is>
+          <t>Phase 6</t>
+        </is>
+      </c>
+      <c r="B137" s="40" t="inlineStr">
+        <is>
+          <t>자동화</t>
+        </is>
+      </c>
+      <c r="C137" s="40" t="inlineStr">
+        <is>
+          <t>6-14</t>
+        </is>
+      </c>
+      <c r="D137" s="41" t="inlineStr">
+        <is>
+          <t>관세 변동 알림/모니터링 (Make + Cron)</t>
+        </is>
+      </c>
+      <c r="E137" s="41" t="inlineStr">
+        <is>
+          <t>app/api/cron/</t>
+        </is>
+      </c>
+      <c r="F137" s="40" t="inlineStr">
+        <is>
+          <t>TODO</t>
+        </is>
+      </c>
+      <c r="G137" s="40" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="H137" s="40" t="inlineStr">
+        <is>
+          <t>3h</t>
+        </is>
+      </c>
+      <c r="I137" s="41" t="inlineStr">
+        <is>
+          <t>Make.com 시나리오 or Vercel Cron. 이메일/Slack 알림</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" s="40" t="inlineStr">
+        <is>
+          <t>Phase 6</t>
+        </is>
+      </c>
+      <c r="B138" s="40" t="inlineStr">
+        <is>
+          <t>AI/LLM</t>
+        </is>
+      </c>
+      <c r="C138" s="40" t="inlineStr">
+        <is>
+          <t>6-15</t>
+        </is>
+      </c>
+      <c r="D138" s="41" t="inlineStr">
+        <is>
+          <t>AI 에이전트 프레임워크 (POTAL SDK)</t>
+        </is>
+      </c>
+      <c r="E138" s="41" t="inlineStr">
+        <is>
+          <t>packages/potal-agent-sdk/</t>
+        </is>
+      </c>
+      <c r="F138" s="40" t="inlineStr">
+        <is>
+          <t>TODO</t>
+        </is>
+      </c>
+      <c r="G138" s="40" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="H138" s="40" t="inlineStr">
+        <is>
+          <t>8h</t>
+        </is>
+      </c>
+      <c r="I138" s="41" t="inlineStr">
+        <is>
+          <t>Avalara ALFA 대응. POTAL 전용 에이전트 SDK</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" s="40" t="inlineStr">
+        <is>
+          <t>Phase 6</t>
+        </is>
+      </c>
+      <c r="B139" s="40" t="inlineStr">
+        <is>
+          <t>요금제</t>
+        </is>
+      </c>
+      <c r="C139" s="40" t="inlineStr">
+        <is>
+          <t>6-16</t>
+        </is>
+      </c>
+      <c r="D139" s="41" t="inlineStr">
+        <is>
+          <t>코드 내 요금제 업데이트 (Free 100/Basic $20/Pro $80/Enterprise $300)</t>
+        </is>
+      </c>
+      <c r="E139" s="41" t="inlineStr">
+        <is>
+          <t>다수 파일</t>
+        </is>
+      </c>
+      <c r="F139" s="40" t="inlineStr">
+        <is>
+          <t>TODO</t>
+        </is>
+      </c>
+      <c r="G139" s="40" t="inlineStr">
+        <is>
+          <t>Critical</t>
+        </is>
+      </c>
+      <c r="H139" s="40" t="inlineStr">
+        <is>
+          <t>4h</t>
+        </is>
+      </c>
+      <c r="I139" s="41" t="inlineStr">
+        <is>
+          <t>plan-checker, pricing, dashboard, i18n 등 전체. LS 승인 후 실행</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" s="40" t="inlineStr">
+        <is>
+          <t>Phase 6</t>
+        </is>
+      </c>
+      <c r="B140" s="40" t="inlineStr">
+        <is>
+          <t>요금제</t>
+        </is>
+      </c>
+      <c r="C140" s="40" t="inlineStr">
+        <is>
+          <t>6-17</t>
+        </is>
+      </c>
+      <c r="D140" s="41" t="inlineStr">
+        <is>
+          <t>Supabase Pro 전환 ($25/월)</t>
+        </is>
+      </c>
+      <c r="E140" s="41" t="inlineStr">
+        <is>
+          <t>Supabase Dashboard</t>
+        </is>
+      </c>
+      <c r="F140" s="40" t="inlineStr">
+        <is>
+          <t>✅ Done</t>
+        </is>
+      </c>
+      <c r="G140" s="40" t="inlineStr">
+        <is>
+          <t>Critical</t>
+        </is>
+      </c>
+      <c r="H140" s="40" t="inlineStr">
+        <is>
+          <t>0.5h</t>
+        </is>
+      </c>
+      <c r="I140" s="41" t="inlineStr">
+        <is>
+          <t>세션 32: Supabase Pro 활성화 확인. 마이그레이션 010-016 실행 완료. Management API (curl) 경유</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>Phase 5</t>
+        </is>
+      </c>
+      <c r="B141" t="inlineStr">
+        <is>
+          <t>관세 데이터</t>
+        </is>
+      </c>
+      <c r="C141" t="inlineStr">
+        <is>
+          <t>5-33</t>
+        </is>
+      </c>
+      <c r="D141" t="inlineStr">
+        <is>
+          <t>trade_remedy 4개 테이블 Supabase 생성 (DDL + 인덱스)</t>
+        </is>
+      </c>
+      <c r="E141" t="inlineStr">
+        <is>
+          <t>Supabase Management API</t>
+        </is>
+      </c>
+      <c r="F141" t="inlineStr">
+        <is>
+          <t>✅ Done</t>
+        </is>
+      </c>
+      <c r="G141" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="H141" t="inlineStr">
+        <is>
+          <t>0.5h</t>
+        </is>
+      </c>
+      <c r="I141" t="inlineStr">
+        <is>
+          <t>세션 33: trade_remedy_cases/products/duties + safeguard_exemptions</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="inlineStr">
+        <is>
+          <t>Phase 5</t>
+        </is>
+      </c>
+      <c r="B142" t="inlineStr">
+        <is>
+          <t>관세 데이터</t>
+        </is>
+      </c>
+      <c r="C142" t="inlineStr">
+        <is>
+          <t>5-34</t>
+        </is>
+      </c>
+      <c r="D142" t="inlineStr">
+        <is>
+          <t>TTBD 반덤핑 데이터 Supabase 임포트 (36개국)</t>
+        </is>
+      </c>
+      <c r="E142" t="inlineStr">
+        <is>
+          <t>import_trade_remedies.py</t>
+        </is>
+      </c>
+      <c r="F142" t="inlineStr">
+        <is>
+          <t>✅ Done</t>
+        </is>
+      </c>
+      <c r="G142" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="H142" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="I142" t="inlineStr">
+        <is>
+          <t>세션 33: AD 9,278 케이스 + 41,714 제품(HS) + 28,285 관세율</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="inlineStr">
+        <is>
+          <t>Phase 5</t>
+        </is>
+      </c>
+      <c r="B143" t="inlineStr">
+        <is>
+          <t>관세 데이터</t>
+        </is>
+      </c>
+      <c r="C143" t="inlineStr">
+        <is>
+          <t>5-35</t>
+        </is>
+      </c>
+      <c r="D143" t="inlineStr">
+        <is>
+          <t>TTBD 상계관세 데이터 Supabase 임포트 (19개국)</t>
+        </is>
+      </c>
+      <c r="E143" t="inlineStr">
+        <is>
+          <t>import_trade_remedies.py</t>
+        </is>
+      </c>
+      <c r="F143" t="inlineStr">
+        <is>
+          <t>✅ Done</t>
+        </is>
+      </c>
+      <c r="G143" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="H143" t="inlineStr">
+        <is>
+          <t>0.5h</t>
+        </is>
+      </c>
+      <c r="I143" t="inlineStr">
+        <is>
+          <t>세션 33: CVD 1,263 케이스 + 8,888 제품(HS) + 5,210 관세율</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="inlineStr">
+        <is>
+          <t>Phase 5</t>
+        </is>
+      </c>
+      <c r="B144" t="inlineStr">
+        <is>
+          <t>관세 데이터</t>
+        </is>
+      </c>
+      <c r="C144" t="inlineStr">
+        <is>
+          <t>5-36</t>
+        </is>
+      </c>
+      <c r="D144" t="inlineStr">
+        <is>
+          <t>WTO 세이프가드 데이터 Supabase 임포트 (글로벌)</t>
+        </is>
+      </c>
+      <c r="E144" t="inlineStr">
+        <is>
+          <t>import_trade_remedies.py</t>
+        </is>
+      </c>
+      <c r="F144" t="inlineStr">
+        <is>
+          <t>✅ Done</t>
+        </is>
+      </c>
+      <c r="G144" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="H144" t="inlineStr">
+        <is>
+          <t>0.5h</t>
+        </is>
+      </c>
+      <c r="I144" t="inlineStr">
+        <is>
+          <t>세션 33: SG 458 케이스 + 4,657 제품 + 4,018 조치 + 15,935 면제국</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="inlineStr">
+        <is>
+          <t>Phase 5</t>
+        </is>
+      </c>
+      <c r="B145" t="inlineStr">
+        <is>
+          <t>관세 데이터</t>
+        </is>
+      </c>
+      <c r="C145" t="inlineStr">
+        <is>
+          <t>5-37</t>
+        </is>
+      </c>
+      <c r="D145" t="inlineStr">
+        <is>
+          <t>lookup_duty_rate에 반덤핑/상계관세/세이프가드 5단계 폴백 추가</t>
+        </is>
+      </c>
+      <c r="E145" t="inlineStr">
+        <is>
+          <t>lookup_duty_rate_v2()</t>
+        </is>
+      </c>
+      <c r="F145" t="inlineStr">
+        <is>
+          <t>TODO</t>
+        </is>
+      </c>
+      <c r="G145" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="H145" t="inlineStr">
+        <is>
+          <t>2h</t>
+        </is>
+      </c>
+      <c r="I145" t="inlineStr">
+        <is>
+          <t>현재 4단계 → 5단계: AD/CVD/SG 추가관세 조회 추가</t>
         </is>
       </c>
     </row>
@@ -5333,7 +7505,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:E8"/>
+  <dimension ref="A1:E9"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="1" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="15" customWidth="1" style="18" min="1" max="1"/>
@@ -5399,7 +7571,7 @@
         <v>38</v>
       </c>
       <c r="C3" s="23" t="n">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="D3" s="23" t="n">
         <v>7</v>
@@ -5423,7 +7595,7 @@
         <v>10</v>
       </c>
       <c r="D4" s="23" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="E4" s="23" t="inlineStr">
         <is>
@@ -5462,10 +7634,10 @@
         <v>11</v>
       </c>
       <c r="C6" s="23" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D6" s="23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E6" s="23" t="inlineStr">
         <is>
@@ -5480,17 +7652,17 @@
         </is>
       </c>
       <c r="B7" s="23" t="n">
-        <v>14</v>
+        <v>34</v>
       </c>
       <c r="C7" s="23" t="n">
-        <v>1</v>
+        <v>19</v>
       </c>
       <c r="D7" s="23" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="E7" s="23" t="inlineStr">
         <is>
-          <t>47.0h</t>
+          <t>69.5h</t>
         </is>
       </c>
     </row>
@@ -5513,6 +7685,27 @@
         <v/>
       </c>
       <c r="E8" s="38" t="n"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="42" t="inlineStr">
+        <is>
+          <t>Phase 6</t>
+        </is>
+      </c>
+      <c r="B9" s="43" t="n">
+        <v>17</v>
+      </c>
+      <c r="C9" s="43" t="n">
+        <v>2</v>
+      </c>
+      <c r="D9" s="43" t="n">
+        <v>15</v>
+      </c>
+      <c r="E9" s="43" t="inlineStr">
+        <is>
+          <t>80.5h</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0" gridLinesSet="1"/>
